--- a/templates/office/EMP_EXE_030_레거시DB연계명세서.xlsx
+++ b/templates/office/EMP_EXE_030_레거시DB연계명세서.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 사내 연구/처방 시스템(ProductLab) - SyncGuard AI 간 API 전문 인터페이스 상세 명세서</t>
+          <t>한빛글로벌 사내 연구/처방 시스템(ProductLab) - SyncGuard AI 간 API 전문 인터페이스 상세 명세서</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 AI 기반 화장품 표시광고 심의 및 리스크 예방 시스템 구축</t>
+          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>(주)아모레퍼시픽 (HANBIT GLOBAL)</t>
+          <t>㈜한빛글로벌 (Hanbit Global Corp.)</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>㈜그로브소프트 (EMPASY)</t>
+          <t>㈜엠파시 (Empasy Inc.)</t>
         </is>
       </c>
     </row>

--- a/templates/office/EMP_EXE_030_레거시DB연계명세서.xlsx
+++ b/templates/office/EMP_EXE_030_레거시DB연계명세서.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문서정보" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProductLab_API명세" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLM_Nexus_API명세" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -508,14 +508,14 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>ProductLab 연 계 명 세 서</t>
+          <t>PLM-Nexus 연 계 명 세 서</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>한빛글로벌 사내 연구/처방 시스템(ProductLab) - SyncGuard AI 간 API 전문 인터페이스 상세 명세서</t>
+          <t>한빛글로벌 사내 연구/설계사양 시스템(PLM-Nexus) - SyncFlow AI 간 API 전문 인터페이스 상세 명세서</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
+          <t>한빛글로벌 지능형 공급망 구매·조달 계약 및 부품 품질규격 AI 검증 플랫폼(SyncFlow AI) 구축</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>ProductLab (사내 처방/원료 연구 시스템)</t>
+          <t>PLM-Nexus (사내 설계사양/원소재 연구 시스템)</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
     <row r="2">
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>ProductLab 연계 REST API 인터페이스 목록</t>
+          <t>PLM-Nexus 연계 REST API 인터페이스 목록</t>
         </is>
       </c>
     </row>
@@ -716,17 +716,17 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>제품 처방 원료 목록 조회</t>
+          <t>제품 설계사양 원소재 목록 조회</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>ProductLab</t>
+          <t>PLM-Nexus</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>ProductLab</t>
+          <t>PLM-Nexus</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>{ productCode, targetClaim, testType }</t>
+          <t>{ productCode, targetSpec, testType }</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>ProductLab</t>
+          <t>PLM-Nexus</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>성분 배합 한도 실시간 검증</t>
+          <t>성분 조성 한도 실시간 검증</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>ProductLab</t>
+          <t>PLM-Nexus</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>ProductLab 성분 마스터 증분 추출</t>
+          <t>PLM-Nexus 성분 마스터 증분 추출</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>ProductLab</t>
+          <t>PLM-Nexus</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -946,27 +946,27 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>/api/v1/claim/sync/result-notify</t>
+          <t>/api/v1/Spec/sync/result-notify</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>광고 심의 완료 상태 역동기화</t>
+          <t>계약·규격 검증 완료 상태 역동기화</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>ProductLab</t>
+          <t>PLM-Nexus</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>{ productCode, claimReqNo, finalStatus, certUsageList }</t>
+          <t>{ productCode, verifyReqNo, finalStatus, certUsageList }</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
